--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42660-2024 artfynd.xlsx
+++ b/artfynd/A 42660-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4242193</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4210821</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
